--- a/public/flashcards/minna_lesson_3.xlsx
+++ b/public/flashcards/minna_lesson_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Endle\Downloads\minna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Chat-Website\public\flashcards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A758472E-BD13-425A-AB19-82551206CA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0447AB16-4507-4F02-9159-9F0A5ED6CAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -431,7 +431,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,9 +465,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -775,439 +774,490 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="27.140625" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3" t="s">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1217,8 +1267,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -1227,7 +1277,7 @@
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1239,61 +1289,6 @@
       </c>
       <c r="D1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
